--- a/data/raw/51301-2026-02-medicaid.xlsx
+++ b/data/raw/51301-2026-02-medicaid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Supplemental Data Tables\2026\February 2026 Baseline\4-PDF and Excel to FTI and Comms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/481781ca8254c580/Desktop/OneDrive Desktop files/Sandboxes/Data_friendly_CBO_Baseline_Detail/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{84A496C8-0FF0-401E-A5FD-37F52A73AA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{84A496C8-0FF0-401E-A5FD-37F52A73AA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E079B21-46EE-4D85-AD1A-91ADE7C3CC65}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F28F857-6D2C-4C32-B2B6-AD7E34D45536}"/>
+    <workbookView xWindow="60" yWindow="26" windowWidth="16457" windowHeight="9454" xr2:uid="{9F28F857-6D2C-4C32-B2B6-AD7E34D45536}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicaid_02-2026" sheetId="1" r:id="rId1"/>
@@ -210,7 +210,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
@@ -632,12 +632,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -664,19 +677,6 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -696,7 +696,9 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{75709B8E-F9A7-4C6F-8918-D91B54EE4FDB}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1075,18 +1077,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD236"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="17" width="8.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.28515625" style="1"/>
-    <col min="19" max="19" width="9.28515625" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.28515625" style="1"/>
+    <col min="3" max="3" width="37.69140625" style="1" customWidth="1"/>
+    <col min="4" max="17" width="8.69140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.3046875" style="1"/>
+    <col min="19" max="19" width="9.3046875" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.3046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
       <c r="B1" s="44"/>
       <c r="C1" s="44"/>
@@ -1105,7 +1107,7 @@
       <c r="P1" s="44"/>
       <c r="Q1" s="44"/>
     </row>
-    <row r="2" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="39" t="s">
@@ -1120,19 +1122,19 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="87" t="s">
+      <c r="M2" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="93"/>
+      <c r="P2" s="93"/>
+      <c r="Q2" s="93"/>
       <c r="R2" s="4"/>
       <c r="V2" s="36"/>
       <c r="W2" s="36"/>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="40" t="s">
@@ -1157,7 +1159,7 @@
       <c r="W3" s="36"/>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1179,7 +1181,7 @@
       <c r="W4" s="36"/>
       <c r="X4" s="36"/>
     </row>
-    <row r="5" spans="1:24" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A5" s="41"/>
       <c r="B5" s="41"/>
       <c r="C5" s="42"/>
@@ -1202,17 +1204,17 @@
       <c r="W5" s="36"/>
       <c r="X5" s="36"/>
     </row>
-    <row r="6" spans="1:24" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="89" t="s">
+    <row r="6" spans="1:24" ht="17.600000000000001" x14ac:dyDescent="0.4">
+      <c r="A6" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
       <c r="I6" s="42"/>
       <c r="J6" s="42"/>
       <c r="K6" s="42"/>
@@ -1226,7 +1228,7 @@
       <c r="W6" s="36"/>
       <c r="X6" s="36"/>
     </row>
-    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10"/>
@@ -1244,16 +1246,16 @@
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
       <c r="O7" s="8"/>
-      <c r="P7" s="90" t="s">
+      <c r="P7" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="Q7" s="90" t="s">
+      <c r="Q7" s="95" t="s">
         <v>37</v>
       </c>
       <c r="R7" s="4"/>
       <c r="S7" s="52"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="13"/>
       <c r="C8" s="14"/>
@@ -1293,10 +1295,10 @@
       <c r="O8" s="54">
         <v>2036</v>
       </c>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="91"/>
-    </row>
-    <row r="9" spans="1:24" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+    </row>
+    <row r="9" spans="1:24" ht="7.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10"/>
@@ -1315,12 +1317,12 @@
       <c r="P9" s="45"/>
       <c r="Q9" s="45"/>
     </row>
-    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="83" t="s">
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
       <c r="D10" s="57"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
@@ -1342,12 +1344,12 @@
       <c r="R10" s="7"/>
       <c r="T10" s="7"/>
     </row>
-    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="95" t="s">
+    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="57"/>
       <c r="E11" s="57"/>
       <c r="F11" s="57"/>
@@ -1365,7 +1367,7 @@
       <c r="R11" s="7"/>
       <c r="T11" s="7"/>
     </row>
-    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="58"/>
       <c r="B12" s="20"/>
       <c r="C12" s="56"/>
@@ -1387,12 +1389,12 @@
       <c r="S12" s="4"/>
       <c r="T12" s="7"/>
     </row>
-    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="83" t="s">
+    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
       <c r="D13" s="70">
         <v>668</v>
       </c>
@@ -1439,7 +1441,7 @@
       <c r="S13" s="4"/>
       <c r="T13" s="7"/>
     </row>
-    <row r="14" spans="1:24" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="58"/>
       <c r="B14" s="20"/>
       <c r="C14" s="56"/>
@@ -1461,12 +1463,12 @@
       <c r="S14" s="4"/>
       <c r="T14" s="7"/>
     </row>
-    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="83" t="s">
+    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
       <c r="D15" s="75"/>
       <c r="E15" s="75"/>
       <c r="F15" s="75"/>
@@ -1485,11 +1487,11 @@
       <c r="S15" s="4"/>
       <c r="T15" s="7"/>
     </row>
-    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="93" t="s">
+    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="93"/>
+      <c r="B16" s="82"/>
       <c r="C16" s="56"/>
       <c r="D16" s="61"/>
       <c r="E16" s="61"/>
@@ -1509,12 +1511,12 @@
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
     </row>
-    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="56"/>
-      <c r="B17" s="82" t="s">
+      <c r="B17" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="82"/>
+      <c r="C17" s="84"/>
       <c r="D17" s="61"/>
       <c r="E17" s="61"/>
       <c r="F17" s="61"/>
@@ -1533,12 +1535,12 @@
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
     </row>
-    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="60"/>
-      <c r="B18" s="94" t="s">
+      <c r="B18" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="94"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="70">
         <v>142</v>
       </c>
@@ -1586,12 +1588,12 @@
       <c r="T18" s="7"/>
       <c r="W18" s="22"/>
     </row>
-    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="56"/>
-      <c r="B19" s="94" t="s">
+      <c r="B19" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="94"/>
+      <c r="C19" s="85"/>
       <c r="D19" s="70">
         <v>295</v>
       </c>
@@ -1638,12 +1640,12 @@
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
     </row>
-    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="56"/>
-      <c r="B20" s="94" t="s">
+      <c r="B20" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="94"/>
+      <c r="C20" s="85"/>
       <c r="D20" s="70">
         <v>16</v>
       </c>
@@ -1690,12 +1692,12 @@
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
     </row>
-    <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="56"/>
-      <c r="B21" s="82" t="s">
+      <c r="B21" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="82"/>
+      <c r="C21" s="84"/>
       <c r="D21" s="61"/>
       <c r="E21" s="61"/>
       <c r="F21" s="61"/>
@@ -1714,12 +1716,12 @@
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
     </row>
-    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="56"/>
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="94"/>
+      <c r="C22" s="85"/>
       <c r="D22" s="70">
         <v>64</v>
       </c>
@@ -1767,12 +1769,12 @@
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
     </row>
-    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="56"/>
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="94"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="72">
         <v>110</v>
       </c>
@@ -1819,7 +1821,7 @@
       <c r="S23" s="4"/>
       <c r="T23" s="7"/>
     </row>
-    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="61"/>
       <c r="C24" s="59" t="s">
         <v>20</v>
@@ -1870,7 +1872,7 @@
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
     </row>
-    <row r="25" spans="1:23" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
       <c r="C25" s="61"/>
@@ -1892,12 +1894,12 @@
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
     </row>
-    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="93" t="s">
+    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="93"/>
-      <c r="C26" s="93"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="82"/>
       <c r="D26" s="70">
         <v>8</v>
       </c>
@@ -1944,12 +1946,12 @@
       <c r="S26" s="7"/>
       <c r="T26" s="7"/>
     </row>
-    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="93" t="s">
+    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="93"/>
-      <c r="C27" s="93"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="82"/>
       <c r="D27" s="70">
         <v>7</v>
       </c>
@@ -1996,12 +1998,12 @@
       <c r="S27" s="34"/>
       <c r="T27" s="7"/>
     </row>
-    <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="93" t="s">
+    <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="93"/>
-      <c r="C28" s="93"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="82"/>
       <c r="D28" s="70">
         <v>27</v>
       </c>
@@ -2049,7 +2051,7 @@
       <c r="T28" s="7"/>
       <c r="W28" s="22"/>
     </row>
-    <row r="29" spans="1:23" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="62"/>
       <c r="B29" s="63"/>
       <c r="C29" s="64"/>
@@ -2071,7 +2073,7 @@
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
     </row>
-    <row r="30" spans="1:23" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
       <c r="C30" s="61"/>
@@ -2093,12 +2095,12 @@
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
     </row>
-    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="97" t="s">
+    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="97"/>
-      <c r="C31" s="97"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="83"/>
       <c r="D31" s="61"/>
       <c r="E31" s="61"/>
       <c r="F31" s="61"/>
@@ -2117,7 +2119,7 @@
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
     </row>
-    <row r="32" spans="1:23" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="58"/>
       <c r="B32" s="20"/>
       <c r="C32" s="56"/>
@@ -2139,14 +2141,14 @@
       <c r="S32" s="7"/>
       <c r="T32" s="7"/>
     </row>
-    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="83" t="s">
+    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
       <c r="F33" s="61"/>
       <c r="G33" s="61"/>
       <c r="H33" s="61"/>
@@ -2163,11 +2165,11 @@
       <c r="S33" s="7"/>
       <c r="T33" s="7"/>
     </row>
-    <row r="34" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="96" t="s">
+    <row r="34" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="96"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="56"/>
       <c r="D34" s="70">
         <v>125</v>
@@ -2215,12 +2217,12 @@
       <c r="S34" s="46"/>
       <c r="T34" s="7"/>
     </row>
-    <row r="35" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="82" t="s">
+    <row r="35" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="82"/>
-      <c r="C35" s="82"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="84"/>
       <c r="D35" s="70">
         <v>191</v>
       </c>
@@ -2267,11 +2269,11 @@
       <c r="S35" s="46"/>
       <c r="T35" s="7"/>
     </row>
-    <row r="36" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="82" t="s">
+    <row r="36" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B36" s="82"/>
+      <c r="B36" s="84"/>
       <c r="C36" s="56"/>
       <c r="D36" s="70">
         <v>85</v>
@@ -2319,12 +2321,12 @@
       <c r="S36" s="46"/>
       <c r="T36" s="7"/>
     </row>
-    <row r="37" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="82" t="s">
+    <row r="37" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="82"/>
-      <c r="C37" s="82"/>
+      <c r="B37" s="84"/>
+      <c r="C37" s="84"/>
       <c r="D37" s="70">
         <v>83</v>
       </c>
@@ -2371,12 +2373,12 @@
       <c r="S37" s="46"/>
       <c r="T37" s="7"/>
     </row>
-    <row r="38" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="82" t="s">
+    <row r="38" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="82"/>
-      <c r="C38" s="82"/>
+      <c r="B38" s="84"/>
+      <c r="C38" s="84"/>
       <c r="D38" s="72">
         <v>144</v>
       </c>
@@ -2423,7 +2425,7 @@
       <c r="S38" s="55"/>
       <c r="T38" s="7"/>
     </row>
-    <row r="39" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="20"/>
       <c r="B39" s="20" t="s">
         <v>20</v>
@@ -2474,7 +2476,7 @@
       <c r="S39" s="46"/>
       <c r="T39" s="7"/>
     </row>
-    <row r="40" spans="1:30" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="59"/>
       <c r="B40" s="59"/>
       <c r="C40" s="56"/>
@@ -2496,14 +2498,14 @@
       <c r="S40" s="7"/>
       <c r="T40" s="7"/>
     </row>
-    <row r="41" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="83" t="s">
+    <row r="41" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="86"/>
       <c r="F41" s="61"/>
       <c r="G41" s="61"/>
       <c r="H41" s="61"/>
@@ -2520,11 +2522,11 @@
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
     </row>
-    <row r="42" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="82" t="s">
+    <row r="42" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="82"/>
+      <c r="B42" s="84"/>
       <c r="C42" s="56"/>
       <c r="D42" s="70">
         <v>8</v>
@@ -2582,12 +2584,12 @@
       <c r="AC42" s="51"/>
       <c r="AD42" s="51"/>
     </row>
-    <row r="43" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="82" t="s">
+    <row r="43" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="82"/>
-      <c r="C43" s="82"/>
+      <c r="B43" s="84"/>
+      <c r="C43" s="84"/>
       <c r="D43" s="70">
         <v>9</v>
       </c>
@@ -2644,11 +2646,11 @@
       <c r="AC43" s="51"/>
       <c r="AD43" s="51"/>
     </row>
-    <row r="44" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="82" t="s">
+    <row r="44" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="82"/>
+      <c r="B44" s="84"/>
       <c r="C44" s="56"/>
       <c r="D44" s="70">
         <v>31</v>
@@ -2706,12 +2708,12 @@
       <c r="AC44" s="51"/>
       <c r="AD44" s="51"/>
     </row>
-    <row r="45" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="82" t="s">
+    <row r="45" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="82"/>
-      <c r="C45" s="82"/>
+      <c r="B45" s="84"/>
+      <c r="C45" s="84"/>
       <c r="D45" s="70">
         <v>17</v>
       </c>
@@ -2768,12 +2770,12 @@
       <c r="AC45" s="51"/>
       <c r="AD45" s="51"/>
     </row>
-    <row r="46" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="82" t="s">
+    <row r="46" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="82"/>
-      <c r="C46" s="82"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="84"/>
       <c r="D46" s="72">
         <v>17</v>
       </c>
@@ -2830,7 +2832,7 @@
       <c r="AC46" s="51"/>
       <c r="AD46" s="51"/>
     </row>
-    <row r="47" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="20"/>
       <c r="B47" s="20" t="s">
         <v>20</v>
@@ -2891,7 +2893,7 @@
       <c r="AC47" s="51"/>
       <c r="AD47" s="51"/>
     </row>
-    <row r="48" spans="1:30" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="62"/>
       <c r="B48" s="63"/>
       <c r="C48" s="64"/>
@@ -2913,7 +2915,7 @@
       <c r="S48" s="7"/>
       <c r="T48" s="7"/>
     </row>
-    <row r="49" spans="1:30" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="20"/>
       <c r="B49" s="67"/>
       <c r="C49" s="56"/>
@@ -2935,12 +2937,12 @@
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
     </row>
-    <row r="50" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="83" t="s">
+    <row r="50" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="83"/>
-      <c r="C50" s="83"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="86"/>
       <c r="D50" s="66"/>
       <c r="E50" s="66"/>
       <c r="F50" s="66"/>
@@ -2969,12 +2971,12 @@
       <c r="AC50" s="46"/>
       <c r="AD50" s="46"/>
     </row>
-    <row r="51" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="82" t="s">
+    <row r="51" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="B51" s="82"/>
-      <c r="C51" s="82"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="84"/>
       <c r="D51" s="70">
         <v>98</v>
       </c>
@@ -3031,7 +3033,7 @@
       <c r="AC51" s="46"/>
       <c r="AD51" s="46"/>
     </row>
-    <row r="52" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="58"/>
       <c r="B52" s="59"/>
       <c r="C52" s="56"/>
@@ -3063,14 +3065,14 @@
       <c r="AC52" s="46"/>
       <c r="AD52" s="46"/>
     </row>
-    <row r="53" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="83" t="s">
+    <row r="53" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="B53" s="83"/>
-      <c r="C53" s="83"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
+      <c r="B53" s="86"/>
+      <c r="C53" s="86"/>
+      <c r="D53" s="86"/>
+      <c r="E53" s="86"/>
       <c r="F53" s="66"/>
       <c r="G53" s="66"/>
       <c r="H53" s="66"/>
@@ -3097,7 +3099,7 @@
       <c r="AC53" s="46"/>
       <c r="AD53" s="46"/>
     </row>
-    <row r="54" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="59" t="s">
         <v>17</v>
       </c>
@@ -3148,7 +3150,7 @@
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
     </row>
-    <row r="55" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="59" t="s">
         <v>18</v>
       </c>
@@ -3199,7 +3201,7 @@
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
     </row>
-    <row r="56" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="59" t="s">
         <v>19</v>
       </c>
@@ -3250,7 +3252,7 @@
       <c r="S56" s="7"/>
       <c r="T56" s="7"/>
     </row>
-    <row r="57" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="59" t="s">
         <v>42</v>
       </c>
@@ -3301,12 +3303,12 @@
       <c r="S57" s="7"/>
       <c r="T57" s="7"/>
     </row>
-    <row r="58" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="82" t="s">
+    <row r="58" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="82"/>
-      <c r="C58" s="82"/>
+      <c r="B58" s="84"/>
+      <c r="C58" s="84"/>
       <c r="D58" s="70">
         <v>8670</v>
       </c>
@@ -3353,7 +3355,7 @@
       <c r="S58" s="7"/>
       <c r="T58" s="7"/>
     </row>
-    <row r="59" spans="1:30" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:30" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="25"/>
       <c r="B59" s="26"/>
       <c r="C59" s="27"/>
@@ -3375,7 +3377,7 @@
       <c r="S59" s="7"/>
       <c r="T59" s="7"/>
     </row>
-    <row r="60" spans="1:30" s="7" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:30" s="7" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -3395,7 +3397,7 @@
       <c r="Q60" s="30"/>
       <c r="R60" s="4"/>
     </row>
-    <row r="61" spans="1:30" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:30" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="17" t="s">
         <v>29</v>
       </c>
@@ -3417,7 +3419,7 @@
       <c r="Q61" s="30"/>
       <c r="R61" s="47"/>
     </row>
-    <row r="62" spans="1:30" s="7" customFormat="1" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" s="7" customFormat="1" ht="4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="31"/>
       <c r="B62" s="19"/>
       <c r="C62" s="32"/>
@@ -3438,157 +3440,157 @@
       <c r="R62" s="47"/>
       <c r="S62" s="47"/>
     </row>
-    <row r="63" spans="1:30" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:30" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B63" s="92" t="s">
+      <c r="B63" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="C63" s="92"/>
-      <c r="D63" s="92"/>
-      <c r="E63" s="92"/>
-      <c r="F63" s="92"/>
-      <c r="G63" s="92"/>
-      <c r="H63" s="92"/>
-      <c r="I63" s="92"/>
-      <c r="J63" s="92"/>
-      <c r="K63" s="92"/>
-      <c r="L63" s="92"/>
-      <c r="M63" s="92"/>
-      <c r="N63" s="92"/>
-      <c r="O63" s="92"/>
-      <c r="P63" s="92"/>
-      <c r="Q63" s="92"/>
+      <c r="C63" s="97"/>
+      <c r="D63" s="97"/>
+      <c r="E63" s="97"/>
+      <c r="F63" s="97"/>
+      <c r="G63" s="97"/>
+      <c r="H63" s="97"/>
+      <c r="I63" s="97"/>
+      <c r="J63" s="97"/>
+      <c r="K63" s="97"/>
+      <c r="L63" s="97"/>
+      <c r="M63" s="97"/>
+      <c r="N63" s="97"/>
+      <c r="O63" s="97"/>
+      <c r="P63" s="97"/>
+      <c r="Q63" s="97"/>
       <c r="R63" s="47"/>
-      <c r="S63" s="86"/>
-      <c r="T63" s="86"/>
-      <c r="U63" s="86"/>
-      <c r="V63" s="86"/>
-      <c r="W63" s="86"/>
-    </row>
-    <row r="64" spans="1:30" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S63" s="91"/>
+      <c r="T63" s="91"/>
+      <c r="U63" s="91"/>
+      <c r="V63" s="91"/>
+      <c r="W63" s="91"/>
+    </row>
+    <row r="64" spans="1:30" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
-      <c r="B64" s="92"/>
-      <c r="C64" s="92"/>
-      <c r="D64" s="92"/>
-      <c r="E64" s="92"/>
-      <c r="F64" s="92"/>
-      <c r="G64" s="92"/>
-      <c r="H64" s="92"/>
-      <c r="I64" s="92"/>
-      <c r="J64" s="92"/>
-      <c r="K64" s="92"/>
-      <c r="L64" s="92"/>
-      <c r="M64" s="92"/>
-      <c r="N64" s="92"/>
-      <c r="O64" s="92"/>
-      <c r="P64" s="92"/>
-      <c r="Q64" s="92"/>
+      <c r="B64" s="97"/>
+      <c r="C64" s="97"/>
+      <c r="D64" s="97"/>
+      <c r="E64" s="97"/>
+      <c r="F64" s="97"/>
+      <c r="G64" s="97"/>
+      <c r="H64" s="97"/>
+      <c r="I64" s="97"/>
+      <c r="J64" s="97"/>
+      <c r="K64" s="97"/>
+      <c r="L64" s="97"/>
+      <c r="M64" s="97"/>
+      <c r="N64" s="97"/>
+      <c r="O64" s="97"/>
+      <c r="P64" s="97"/>
+      <c r="Q64" s="97"/>
       <c r="R64" s="47"/>
       <c r="S64" s="47"/>
     </row>
-    <row r="65" spans="1:25" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B65" s="85" t="s">
+      <c r="B65" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="C65" s="85"/>
-      <c r="D65" s="85"/>
-      <c r="E65" s="85"/>
-      <c r="F65" s="85"/>
-      <c r="G65" s="85"/>
-      <c r="H65" s="85"/>
-      <c r="I65" s="85"/>
-      <c r="J65" s="85"/>
-      <c r="K65" s="85"/>
-      <c r="L65" s="85"/>
-      <c r="M65" s="85"/>
-      <c r="N65" s="85"/>
-      <c r="O65" s="85"/>
-      <c r="P65" s="85"/>
-      <c r="Q65" s="85"/>
+      <c r="C65" s="90"/>
+      <c r="D65" s="90"/>
+      <c r="E65" s="90"/>
+      <c r="F65" s="90"/>
+      <c r="G65" s="90"/>
+      <c r="H65" s="90"/>
+      <c r="I65" s="90"/>
+      <c r="J65" s="90"/>
+      <c r="K65" s="90"/>
+      <c r="L65" s="90"/>
+      <c r="M65" s="90"/>
+      <c r="N65" s="90"/>
+      <c r="O65" s="90"/>
+      <c r="P65" s="90"/>
+      <c r="Q65" s="90"/>
       <c r="R65" s="47"/>
-      <c r="S65" s="84"/>
-      <c r="T65" s="84"/>
-      <c r="U65" s="84"/>
-      <c r="V65" s="84"/>
-      <c r="W65" s="84"/>
-      <c r="X65" s="84"/>
-      <c r="Y65" s="84"/>
-    </row>
-    <row r="66" spans="1:25" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S65" s="89"/>
+      <c r="T65" s="89"/>
+      <c r="U65" s="89"/>
+      <c r="V65" s="89"/>
+      <c r="W65" s="89"/>
+      <c r="X65" s="89"/>
+      <c r="Y65" s="89"/>
+    </row>
+    <row r="66" spans="1:25" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
-      <c r="B66" s="85"/>
-      <c r="C66" s="85"/>
-      <c r="D66" s="85"/>
-      <c r="E66" s="85"/>
-      <c r="F66" s="85"/>
-      <c r="G66" s="85"/>
-      <c r="H66" s="85"/>
-      <c r="I66" s="85"/>
-      <c r="J66" s="85"/>
-      <c r="K66" s="85"/>
-      <c r="L66" s="85"/>
-      <c r="M66" s="85"/>
-      <c r="N66" s="85"/>
-      <c r="O66" s="85"/>
-      <c r="P66" s="85"/>
-      <c r="Q66" s="85"/>
+      <c r="B66" s="90"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="90"/>
+      <c r="E66" s="90"/>
+      <c r="F66" s="90"/>
+      <c r="G66" s="90"/>
+      <c r="H66" s="90"/>
+      <c r="I66" s="90"/>
+      <c r="J66" s="90"/>
+      <c r="K66" s="90"/>
+      <c r="L66" s="90"/>
+      <c r="M66" s="90"/>
+      <c r="N66" s="90"/>
+      <c r="O66" s="90"/>
+      <c r="P66" s="90"/>
+      <c r="Q66" s="90"/>
       <c r="R66" s="47"/>
       <c r="S66" s="47"/>
     </row>
-    <row r="67" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B67" s="85" t="s">
+      <c r="B67" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="85"/>
-      <c r="D67" s="85"/>
-      <c r="E67" s="85"/>
-      <c r="F67" s="85"/>
-      <c r="G67" s="85"/>
-      <c r="H67" s="85"/>
-      <c r="I67" s="85"/>
-      <c r="J67" s="85"/>
-      <c r="K67" s="85"/>
-      <c r="L67" s="85"/>
-      <c r="M67" s="85"/>
-      <c r="N67" s="85"/>
-      <c r="O67" s="85"/>
-      <c r="P67" s="85"/>
-      <c r="Q67" s="85"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="90"/>
+      <c r="E67" s="90"/>
+      <c r="F67" s="90"/>
+      <c r="G67" s="90"/>
+      <c r="H67" s="90"/>
+      <c r="I67" s="90"/>
+      <c r="J67" s="90"/>
+      <c r="K67" s="90"/>
+      <c r="L67" s="90"/>
+      <c r="M67" s="90"/>
+      <c r="N67" s="90"/>
+      <c r="O67" s="90"/>
+      <c r="P67" s="90"/>
+      <c r="Q67" s="90"/>
       <c r="R67" s="7"/>
       <c r="S67" s="4"/>
       <c r="T67" s="7"/>
     </row>
-    <row r="68" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="8"/>
-      <c r="B68" s="85"/>
-      <c r="C68" s="85"/>
-      <c r="D68" s="85"/>
-      <c r="E68" s="85"/>
-      <c r="F68" s="85"/>
-      <c r="G68" s="85"/>
-      <c r="H68" s="85"/>
-      <c r="I68" s="85"/>
-      <c r="J68" s="85"/>
-      <c r="K68" s="85"/>
-      <c r="L68" s="85"/>
-      <c r="M68" s="85"/>
-      <c r="N68" s="85"/>
-      <c r="O68" s="85"/>
-      <c r="P68" s="85"/>
-      <c r="Q68" s="85"/>
+      <c r="B68" s="90"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="90"/>
+      <c r="E68" s="90"/>
+      <c r="F68" s="90"/>
+      <c r="G68" s="90"/>
+      <c r="H68" s="90"/>
+      <c r="I68" s="90"/>
+      <c r="J68" s="90"/>
+      <c r="K68" s="90"/>
+      <c r="L68" s="90"/>
+      <c r="M68" s="90"/>
+      <c r="N68" s="90"/>
+      <c r="O68" s="90"/>
+      <c r="P68" s="90"/>
+      <c r="Q68" s="90"/>
       <c r="R68" s="7"/>
       <c r="S68" s="7"/>
       <c r="T68" s="7"/>
     </row>
-    <row r="69" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="7"/>
       <c r="B69" s="80"/>
       <c r="C69" s="80"/>
@@ -3610,7 +3612,7 @@
       <c r="S69" s="7"/>
       <c r="T69" s="7"/>
     </row>
-    <row r="70" spans="1:25" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="81"/>
       <c r="B70" s="81"/>
       <c r="C70" s="81"/>
@@ -3632,7 +3634,7 @@
       <c r="S70" s="7"/>
       <c r="T70" s="7"/>
     </row>
-    <row r="71" spans="1:25" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="33"/>
@@ -3654,7 +3656,7 @@
       <c r="S71" s="7"/>
       <c r="T71" s="7"/>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="20"/>
@@ -3676,7 +3678,7 @@
       <c r="S72" s="7"/>
       <c r="T72" s="7"/>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="20"/>
@@ -3698,7 +3700,7 @@
       <c r="S73" s="7"/>
       <c r="T73" s="7"/>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -3720,7 +3722,7 @@
       <c r="S74" s="7"/>
       <c r="T74" s="7"/>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -3739,7 +3741,7 @@
       <c r="P75" s="7"/>
       <c r="Q75" s="7"/>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -3758,7 +3760,7 @@
       <c r="P76" s="7"/>
       <c r="Q76" s="7"/>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -3777,7 +3779,7 @@
       <c r="P77" s="7"/>
       <c r="Q77" s="7"/>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -3796,7 +3798,7 @@
       <c r="P78" s="7"/>
       <c r="Q78" s="7"/>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -3815,7 +3817,7 @@
       <c r="P79" s="7"/>
       <c r="Q79" s="7"/>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -3834,7 +3836,7 @@
       <c r="P80" s="7"/>
       <c r="Q80" s="7"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -3853,7 +3855,7 @@
       <c r="P81" s="7"/>
       <c r="Q81" s="7"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -3872,7 +3874,7 @@
       <c r="P82" s="7"/>
       <c r="Q82" s="7"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D83" s="50"/>
       <c r="E83" s="50"/>
       <c r="F83" s="50"/>
@@ -3886,7 +3888,7 @@
       <c r="N83" s="50"/>
       <c r="O83" s="50"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D84" s="50"/>
       <c r="E84" s="50"/>
       <c r="F84" s="50"/>
@@ -3900,7 +3902,7 @@
       <c r="N84" s="50"/>
       <c r="O84" s="50"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D85" s="50"/>
       <c r="E85" s="50"/>
       <c r="F85" s="50"/>
@@ -3914,7 +3916,7 @@
       <c r="N85" s="50"/>
       <c r="O85" s="50"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D86" s="50"/>
       <c r="E86" s="50"/>
       <c r="F86" s="50"/>
@@ -3928,7 +3930,7 @@
       <c r="N86" s="50"/>
       <c r="O86" s="50"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D87" s="50"/>
       <c r="E87" s="50"/>
       <c r="F87" s="50"/>
@@ -3942,7 +3944,7 @@
       <c r="N87" s="50"/>
       <c r="O87" s="50"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D88" s="50"/>
       <c r="E88" s="50"/>
       <c r="F88" s="50"/>
@@ -3956,7 +3958,7 @@
       <c r="N88" s="50"/>
       <c r="O88" s="50"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D89" s="50"/>
       <c r="E89" s="50"/>
       <c r="F89" s="50"/>
@@ -3970,7 +3972,7 @@
       <c r="N89" s="50"/>
       <c r="O89" s="50"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D90" s="50"/>
       <c r="E90" s="50"/>
       <c r="F90" s="50"/>
@@ -3984,7 +3986,7 @@
       <c r="N90" s="50"/>
       <c r="O90" s="50"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D91" s="50"/>
       <c r="E91" s="50"/>
       <c r="F91" s="50"/>
@@ -3998,7 +4000,7 @@
       <c r="N91" s="50"/>
       <c r="O91" s="50"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D92" s="50"/>
       <c r="E92" s="50"/>
       <c r="F92" s="50"/>
@@ -4012,7 +4014,7 @@
       <c r="N92" s="50"/>
       <c r="O92" s="50"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
       <c r="F93" s="50"/>
@@ -4026,7 +4028,7 @@
       <c r="N93" s="50"/>
       <c r="O93" s="50"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D94" s="50"/>
       <c r="E94" s="50"/>
       <c r="F94" s="50"/>
@@ -4040,7 +4042,7 @@
       <c r="N94" s="50"/>
       <c r="O94" s="50"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D95" s="50"/>
       <c r="E95" s="50"/>
       <c r="F95" s="50"/>
@@ -4054,7 +4056,7 @@
       <c r="N95" s="50"/>
       <c r="O95" s="50"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D96" s="50"/>
       <c r="E96" s="50"/>
       <c r="F96" s="50"/>
@@ -4068,7 +4070,7 @@
       <c r="N96" s="50"/>
       <c r="O96" s="50"/>
     </row>
-    <row r="97" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D97" s="50"/>
       <c r="E97" s="50"/>
       <c r="F97" s="50"/>
@@ -4082,7 +4084,7 @@
       <c r="N97" s="50"/>
       <c r="O97" s="50"/>
     </row>
-    <row r="98" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="98" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D98" s="50"/>
       <c r="E98" s="50"/>
       <c r="F98" s="50"/>
@@ -4096,7 +4098,7 @@
       <c r="N98" s="50"/>
       <c r="O98" s="50"/>
     </row>
-    <row r="99" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="99" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D99" s="50"/>
       <c r="E99" s="50"/>
       <c r="F99" s="50"/>
@@ -4110,7 +4112,7 @@
       <c r="N99" s="50"/>
       <c r="O99" s="50"/>
     </row>
-    <row r="100" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="100" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D100" s="50"/>
       <c r="E100" s="50"/>
       <c r="F100" s="50"/>
@@ -4124,7 +4126,7 @@
       <c r="N100" s="50"/>
       <c r="O100" s="50"/>
     </row>
-    <row r="101" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D101" s="50"/>
       <c r="E101" s="50"/>
       <c r="F101" s="50"/>
@@ -4138,7 +4140,7 @@
       <c r="N101" s="50"/>
       <c r="O101" s="50"/>
     </row>
-    <row r="102" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D102" s="50"/>
       <c r="E102" s="50"/>
       <c r="F102" s="50"/>
@@ -4152,7 +4154,7 @@
       <c r="N102" s="50"/>
       <c r="O102" s="50"/>
     </row>
-    <row r="103" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="103" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D103" s="50"/>
       <c r="E103" s="50"/>
       <c r="F103" s="50"/>
@@ -4166,7 +4168,7 @@
       <c r="N103" s="50"/>
       <c r="O103" s="50"/>
     </row>
-    <row r="104" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="104" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D104" s="50"/>
       <c r="E104" s="50"/>
       <c r="F104" s="50"/>
@@ -4180,7 +4182,7 @@
       <c r="N104" s="50"/>
       <c r="O104" s="50"/>
     </row>
-    <row r="105" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="105" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D105" s="50"/>
       <c r="E105" s="50"/>
       <c r="F105" s="50"/>
@@ -4194,7 +4196,7 @@
       <c r="N105" s="50"/>
       <c r="O105" s="50"/>
     </row>
-    <row r="106" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="106" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D106" s="50"/>
       <c r="E106" s="50"/>
       <c r="F106" s="50"/>
@@ -4208,7 +4210,7 @@
       <c r="N106" s="50"/>
       <c r="O106" s="50"/>
     </row>
-    <row r="107" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="107" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D107" s="50"/>
       <c r="E107" s="50"/>
       <c r="F107" s="50"/>
@@ -4222,7 +4224,7 @@
       <c r="N107" s="50"/>
       <c r="O107" s="50"/>
     </row>
-    <row r="108" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="108" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D108" s="50"/>
       <c r="E108" s="50"/>
       <c r="F108" s="50"/>
@@ -4236,7 +4238,7 @@
       <c r="N108" s="50"/>
       <c r="O108" s="50"/>
     </row>
-    <row r="109" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="109" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D109" s="50"/>
       <c r="E109" s="50"/>
       <c r="F109" s="50"/>
@@ -4250,7 +4252,7 @@
       <c r="N109" s="50"/>
       <c r="O109" s="50"/>
     </row>
-    <row r="110" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="110" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D110" s="50"/>
       <c r="E110" s="50"/>
       <c r="F110" s="50"/>
@@ -4264,7 +4266,7 @@
       <c r="N110" s="50"/>
       <c r="O110" s="50"/>
     </row>
-    <row r="111" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="111" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D111" s="50"/>
       <c r="E111" s="50"/>
       <c r="F111" s="50"/>
@@ -4278,7 +4280,7 @@
       <c r="N111" s="50"/>
       <c r="O111" s="50"/>
     </row>
-    <row r="112" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="112" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D112" s="50"/>
       <c r="E112" s="50"/>
       <c r="F112" s="50"/>
@@ -4292,7 +4294,7 @@
       <c r="N112" s="50"/>
       <c r="O112" s="50"/>
     </row>
-    <row r="115" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="115" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D115" s="50"/>
       <c r="E115" s="50"/>
       <c r="F115" s="50"/>
@@ -4306,7 +4308,7 @@
       <c r="N115" s="50"/>
       <c r="O115" s="50"/>
     </row>
-    <row r="116" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="116" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D116" s="50"/>
       <c r="E116" s="50"/>
       <c r="F116" s="50"/>
@@ -4320,7 +4322,7 @@
       <c r="N116" s="50"/>
       <c r="O116" s="50"/>
     </row>
-    <row r="117" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="117" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D117" s="50"/>
       <c r="E117" s="50"/>
       <c r="F117" s="50"/>
@@ -4334,7 +4336,7 @@
       <c r="N117" s="50"/>
       <c r="O117" s="50"/>
     </row>
-    <row r="118" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="118" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D118" s="50"/>
       <c r="E118" s="50"/>
       <c r="F118" s="50"/>
@@ -4348,7 +4350,7 @@
       <c r="N118" s="50"/>
       <c r="O118" s="50"/>
     </row>
-    <row r="119" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="119" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D119" s="50"/>
       <c r="E119" s="50"/>
       <c r="F119" s="50"/>
@@ -4362,7 +4364,7 @@
       <c r="N119" s="50"/>
       <c r="O119" s="50"/>
     </row>
-    <row r="121" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="121" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
       <c r="F121" s="48"/>
@@ -4376,7 +4378,7 @@
       <c r="N121" s="48"/>
       <c r="O121" s="48"/>
     </row>
-    <row r="122" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="122" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
       <c r="F122" s="48"/>
@@ -4390,7 +4392,7 @@
       <c r="N122" s="48"/>
       <c r="O122" s="48"/>
     </row>
-    <row r="123" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="123" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
       <c r="F123" s="48"/>
@@ -4404,7 +4406,7 @@
       <c r="N123" s="48"/>
       <c r="O123" s="48"/>
     </row>
-    <row r="124" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="124" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
       <c r="F124" s="48"/>
@@ -4418,7 +4420,7 @@
       <c r="N124" s="48"/>
       <c r="O124" s="48"/>
     </row>
-    <row r="125" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="125" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
       <c r="F125" s="48"/>
@@ -4432,7 +4434,7 @@
       <c r="N125" s="48"/>
       <c r="O125" s="48"/>
     </row>
-    <row r="126" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="126" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
       <c r="F126" s="48"/>
@@ -4446,7 +4448,7 @@
       <c r="N126" s="48"/>
       <c r="O126" s="48"/>
     </row>
-    <row r="127" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="127" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
       <c r="F127" s="48"/>
@@ -4460,7 +4462,7 @@
       <c r="N127" s="48"/>
       <c r="O127" s="48"/>
     </row>
-    <row r="128" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="128" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
       <c r="F128" s="48"/>
@@ -4474,7 +4476,7 @@
       <c r="N128" s="48"/>
       <c r="O128" s="48"/>
     </row>
-    <row r="129" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="129" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
       <c r="F129" s="48"/>
@@ -4488,7 +4490,7 @@
       <c r="N129" s="48"/>
       <c r="O129" s="48"/>
     </row>
-    <row r="130" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="130" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
       <c r="F130" s="48"/>
@@ -4502,7 +4504,7 @@
       <c r="N130" s="48"/>
       <c r="O130" s="48"/>
     </row>
-    <row r="131" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="131" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D131" s="48"/>
       <c r="E131" s="48"/>
       <c r="F131" s="48"/>
@@ -4516,7 +4518,7 @@
       <c r="N131" s="48"/>
       <c r="O131" s="48"/>
     </row>
-    <row r="132" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="132" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D132" s="48"/>
       <c r="E132" s="48"/>
       <c r="F132" s="48"/>
@@ -4530,7 +4532,7 @@
       <c r="N132" s="48"/>
       <c r="O132" s="48"/>
     </row>
-    <row r="133" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="133" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D133" s="48"/>
       <c r="E133" s="48"/>
       <c r="F133" s="48"/>
@@ -4544,7 +4546,7 @@
       <c r="N133" s="48"/>
       <c r="O133" s="48"/>
     </row>
-    <row r="134" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="134" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D134" s="48"/>
       <c r="E134" s="48"/>
       <c r="F134" s="48"/>
@@ -4558,7 +4560,7 @@
       <c r="N134" s="48"/>
       <c r="O134" s="48"/>
     </row>
-    <row r="135" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="135" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D135" s="48"/>
       <c r="E135" s="48"/>
       <c r="F135" s="48"/>
@@ -4572,7 +4574,7 @@
       <c r="N135" s="48"/>
       <c r="O135" s="48"/>
     </row>
-    <row r="136" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="136" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D136" s="48"/>
       <c r="E136" s="48"/>
       <c r="F136" s="48"/>
@@ -4586,7 +4588,7 @@
       <c r="N136" s="48"/>
       <c r="O136" s="48"/>
     </row>
-    <row r="137" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="137" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D137" s="48"/>
       <c r="E137" s="48"/>
       <c r="F137" s="48"/>
@@ -4600,7 +4602,7 @@
       <c r="N137" s="48"/>
       <c r="O137" s="48"/>
     </row>
-    <row r="138" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="138" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D138" s="48"/>
       <c r="E138" s="48"/>
       <c r="F138" s="48"/>
@@ -4614,7 +4616,7 @@
       <c r="N138" s="48"/>
       <c r="O138" s="48"/>
     </row>
-    <row r="139" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="139" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D139" s="48"/>
       <c r="E139" s="48"/>
       <c r="F139" s="48"/>
@@ -4628,7 +4630,7 @@
       <c r="N139" s="48"/>
       <c r="O139" s="48"/>
     </row>
-    <row r="140" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="140" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D140" s="48"/>
       <c r="E140" s="48"/>
       <c r="F140" s="48"/>
@@ -4642,7 +4644,7 @@
       <c r="N140" s="48"/>
       <c r="O140" s="48"/>
     </row>
-    <row r="141" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="141" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D141" s="48"/>
       <c r="E141" s="48"/>
       <c r="F141" s="48"/>
@@ -4656,7 +4658,7 @@
       <c r="N141" s="48"/>
       <c r="O141" s="48"/>
     </row>
-    <row r="142" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="142" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D142" s="48"/>
       <c r="E142" s="48"/>
       <c r="F142" s="48"/>
@@ -4670,7 +4672,7 @@
       <c r="N142" s="48"/>
       <c r="O142" s="48"/>
     </row>
-    <row r="143" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="143" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D143" s="48"/>
       <c r="E143" s="48"/>
       <c r="F143" s="48"/>
@@ -4684,7 +4686,7 @@
       <c r="N143" s="48"/>
       <c r="O143" s="48"/>
     </row>
-    <row r="144" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="144" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D144" s="48"/>
       <c r="E144" s="48"/>
       <c r="F144" s="48"/>
@@ -4698,7 +4700,7 @@
       <c r="N144" s="48"/>
       <c r="O144" s="48"/>
     </row>
-    <row r="145" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="145" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D145" s="48"/>
       <c r="E145" s="48"/>
       <c r="F145" s="48"/>
@@ -4712,7 +4714,7 @@
       <c r="N145" s="48"/>
       <c r="O145" s="48"/>
     </row>
-    <row r="146" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="146" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D146" s="48"/>
       <c r="E146" s="48"/>
       <c r="F146" s="48"/>
@@ -4726,7 +4728,7 @@
       <c r="N146" s="48"/>
       <c r="O146" s="48"/>
     </row>
-    <row r="147" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="147" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D147" s="48"/>
       <c r="E147" s="48"/>
       <c r="F147" s="48"/>
@@ -4740,7 +4742,7 @@
       <c r="N147" s="48"/>
       <c r="O147" s="48"/>
     </row>
-    <row r="148" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="148" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D148" s="48"/>
       <c r="E148" s="48"/>
       <c r="F148" s="48"/>
@@ -4754,7 +4756,7 @@
       <c r="N148" s="48"/>
       <c r="O148" s="48"/>
     </row>
-    <row r="149" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="149" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D149" s="48"/>
       <c r="E149" s="48"/>
       <c r="F149" s="48"/>
@@ -4768,7 +4770,7 @@
       <c r="N149" s="48"/>
       <c r="O149" s="48"/>
     </row>
-    <row r="150" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="150" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D150" s="48"/>
       <c r="E150" s="48"/>
       <c r="F150" s="48"/>
@@ -4782,7 +4784,7 @@
       <c r="N150" s="48"/>
       <c r="O150" s="48"/>
     </row>
-    <row r="151" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="151" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D151" s="48"/>
       <c r="E151" s="48"/>
       <c r="F151" s="48"/>
@@ -4796,7 +4798,7 @@
       <c r="N151" s="48"/>
       <c r="O151" s="48"/>
     </row>
-    <row r="152" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D152" s="48"/>
       <c r="E152" s="48"/>
       <c r="F152" s="48"/>
@@ -4810,7 +4812,7 @@
       <c r="N152" s="48"/>
       <c r="O152" s="48"/>
     </row>
-    <row r="153" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="153" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D153" s="48"/>
       <c r="E153" s="48"/>
       <c r="F153" s="48"/>
@@ -4824,7 +4826,7 @@
       <c r="N153" s="48"/>
       <c r="O153" s="48"/>
     </row>
-    <row r="154" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="154" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D154" s="48"/>
       <c r="E154" s="48"/>
       <c r="F154" s="48"/>
@@ -4838,7 +4840,7 @@
       <c r="N154" s="48"/>
       <c r="O154" s="48"/>
     </row>
-    <row r="155" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D155" s="48"/>
       <c r="E155" s="48"/>
       <c r="F155" s="48"/>
@@ -4852,7 +4854,7 @@
       <c r="N155" s="48"/>
       <c r="O155" s="48"/>
     </row>
-    <row r="156" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="156" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D156" s="48"/>
       <c r="E156" s="48"/>
       <c r="F156" s="48"/>
@@ -4866,7 +4868,7 @@
       <c r="N156" s="48"/>
       <c r="O156" s="48"/>
     </row>
-    <row r="157" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="157" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D157" s="48"/>
       <c r="E157" s="48"/>
       <c r="F157" s="48"/>
@@ -4880,7 +4882,7 @@
       <c r="N157" s="48"/>
       <c r="O157" s="48"/>
     </row>
-    <row r="158" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="158" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D158" s="48"/>
       <c r="E158" s="48"/>
       <c r="F158" s="48"/>
@@ -4894,7 +4896,7 @@
       <c r="N158" s="48"/>
       <c r="O158" s="48"/>
     </row>
-    <row r="159" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="159" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D159" s="48"/>
       <c r="E159" s="48"/>
       <c r="F159" s="48"/>
@@ -4908,7 +4910,7 @@
       <c r="N159" s="48"/>
       <c r="O159" s="48"/>
     </row>
-    <row r="160" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="160" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D160" s="48"/>
       <c r="E160" s="48"/>
       <c r="F160" s="48"/>
@@ -4922,7 +4924,7 @@
       <c r="N160" s="48"/>
       <c r="O160" s="48"/>
     </row>
-    <row r="161" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="161" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D161" s="48"/>
       <c r="E161" s="48"/>
       <c r="F161" s="48"/>
@@ -4936,7 +4938,7 @@
       <c r="N161" s="48"/>
       <c r="O161" s="48"/>
     </row>
-    <row r="162" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="162" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D162" s="48"/>
       <c r="E162" s="48"/>
       <c r="F162" s="48"/>
@@ -4950,7 +4952,7 @@
       <c r="N162" s="48"/>
       <c r="O162" s="48"/>
     </row>
-    <row r="163" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="163" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D163" s="48"/>
       <c r="E163" s="48"/>
       <c r="F163" s="48"/>
@@ -4964,7 +4966,7 @@
       <c r="N163" s="48"/>
       <c r="O163" s="48"/>
     </row>
-    <row r="164" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="164" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D164" s="48"/>
       <c r="E164" s="48"/>
       <c r="F164" s="48"/>
@@ -4978,7 +4980,7 @@
       <c r="N164" s="48"/>
       <c r="O164" s="48"/>
     </row>
-    <row r="165" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="165" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D165" s="48"/>
       <c r="E165" s="48"/>
       <c r="F165" s="48"/>
@@ -4992,7 +4994,7 @@
       <c r="N165" s="48"/>
       <c r="O165" s="48"/>
     </row>
-    <row r="166" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="166" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D166" s="48"/>
       <c r="E166" s="48"/>
       <c r="F166" s="48"/>
@@ -5006,7 +5008,7 @@
       <c r="N166" s="48"/>
       <c r="O166" s="48"/>
     </row>
-    <row r="167" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="167" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D167" s="48"/>
       <c r="E167" s="48"/>
       <c r="F167" s="48"/>
@@ -5020,7 +5022,7 @@
       <c r="N167" s="48"/>
       <c r="O167" s="48"/>
     </row>
-    <row r="168" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="168" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D168" s="48"/>
       <c r="E168" s="48"/>
       <c r="F168" s="48"/>
@@ -5034,7 +5036,7 @@
       <c r="N168" s="48"/>
       <c r="O168" s="48"/>
     </row>
-    <row r="169" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="169" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D169" s="48"/>
       <c r="E169" s="48"/>
       <c r="F169" s="48"/>
@@ -5048,7 +5050,7 @@
       <c r="N169" s="48"/>
       <c r="O169" s="48"/>
     </row>
-    <row r="170" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="170" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D170" s="48"/>
       <c r="E170" s="48"/>
       <c r="F170" s="48"/>
@@ -5062,7 +5064,7 @@
       <c r="N170" s="48"/>
       <c r="O170" s="48"/>
     </row>
-    <row r="171" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="171" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D171" s="48"/>
       <c r="E171" s="48"/>
       <c r="F171" s="48"/>
@@ -5076,7 +5078,7 @@
       <c r="N171" s="48"/>
       <c r="O171" s="48"/>
     </row>
-    <row r="172" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="172" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D172" s="48"/>
       <c r="E172" s="48"/>
       <c r="F172" s="48"/>
@@ -5090,7 +5092,7 @@
       <c r="N172" s="48"/>
       <c r="O172" s="48"/>
     </row>
-    <row r="173" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="173" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D173" s="48"/>
       <c r="E173" s="48"/>
       <c r="F173" s="48"/>
@@ -5104,7 +5106,7 @@
       <c r="N173" s="48"/>
       <c r="O173" s="48"/>
     </row>
-    <row r="174" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="174" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D174" s="48"/>
       <c r="E174" s="48"/>
       <c r="F174" s="48"/>
@@ -5118,7 +5120,7 @@
       <c r="N174" s="48"/>
       <c r="O174" s="48"/>
     </row>
-    <row r="175" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="175" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D175" s="48"/>
       <c r="E175" s="48"/>
       <c r="F175" s="48"/>
@@ -5132,7 +5134,7 @@
       <c r="N175" s="48"/>
       <c r="O175" s="48"/>
     </row>
-    <row r="176" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="176" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D176" s="48"/>
       <c r="E176" s="48"/>
       <c r="F176" s="48"/>
@@ -5146,7 +5148,7 @@
       <c r="N176" s="48"/>
       <c r="O176" s="48"/>
     </row>
-    <row r="177" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D177" s="48"/>
       <c r="E177" s="48"/>
       <c r="F177" s="48"/>
@@ -5160,7 +5162,7 @@
       <c r="N177" s="48"/>
       <c r="O177" s="48"/>
     </row>
-    <row r="178" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D178" s="48"/>
       <c r="E178" s="48"/>
       <c r="F178" s="48"/>
@@ -5174,7 +5176,7 @@
       <c r="N178" s="48"/>
       <c r="O178" s="48"/>
     </row>
-    <row r="179" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D179" s="48"/>
       <c r="E179" s="48"/>
       <c r="F179" s="48"/>
@@ -5188,7 +5190,7 @@
       <c r="N179" s="48"/>
       <c r="O179" s="48"/>
     </row>
-    <row r="180" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D180" s="48"/>
       <c r="E180" s="48"/>
       <c r="F180" s="48"/>
@@ -5202,7 +5204,7 @@
       <c r="N180" s="48"/>
       <c r="O180" s="48"/>
     </row>
-    <row r="181" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D181" s="48"/>
       <c r="E181" s="48"/>
       <c r="F181" s="48"/>
@@ -5216,7 +5218,7 @@
       <c r="N181" s="48"/>
       <c r="O181" s="48"/>
     </row>
-    <row r="182" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D182" s="48"/>
       <c r="E182" s="48"/>
       <c r="F182" s="48"/>
@@ -5230,7 +5232,7 @@
       <c r="N182" s="48"/>
       <c r="O182" s="48"/>
     </row>
-    <row r="183" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D183" s="48"/>
       <c r="E183" s="48"/>
       <c r="F183" s="48"/>
@@ -5244,7 +5246,7 @@
       <c r="N183" s="48"/>
       <c r="O183" s="48"/>
     </row>
-    <row r="184" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D184" s="48"/>
       <c r="E184" s="48"/>
       <c r="F184" s="48"/>
@@ -5258,7 +5260,7 @@
       <c r="N184" s="48"/>
       <c r="O184" s="48"/>
     </row>
-    <row r="185" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D185" s="48"/>
       <c r="E185" s="48"/>
       <c r="F185" s="48"/>
@@ -5272,7 +5274,7 @@
       <c r="N185" s="48"/>
       <c r="O185" s="48"/>
     </row>
-    <row r="186" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D186" s="48"/>
       <c r="E186" s="48"/>
       <c r="F186" s="48"/>
@@ -5286,7 +5288,7 @@
       <c r="N186" s="48"/>
       <c r="O186" s="48"/>
     </row>
-    <row r="187" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D187" s="48"/>
       <c r="E187" s="48"/>
       <c r="F187" s="48"/>
@@ -5300,7 +5302,7 @@
       <c r="N187" s="48"/>
       <c r="O187" s="48"/>
     </row>
-    <row r="188" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D188" s="48"/>
       <c r="E188" s="48"/>
       <c r="F188" s="48"/>
@@ -5314,7 +5316,7 @@
       <c r="N188" s="48"/>
       <c r="O188" s="48"/>
     </row>
-    <row r="189" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D189" s="48"/>
       <c r="E189" s="48"/>
       <c r="F189" s="48"/>
@@ -5328,7 +5330,7 @@
       <c r="N189" s="48"/>
       <c r="O189" s="48"/>
     </row>
-    <row r="190" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D190" s="48"/>
       <c r="E190" s="48"/>
       <c r="F190" s="48"/>
@@ -5342,7 +5344,7 @@
       <c r="N190" s="48"/>
       <c r="O190" s="48"/>
     </row>
-    <row r="191" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D191" s="48"/>
       <c r="E191" s="48"/>
       <c r="F191" s="48"/>
@@ -5356,7 +5358,7 @@
       <c r="N191" s="48"/>
       <c r="O191" s="48"/>
     </row>
-    <row r="192" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D192" s="48"/>
       <c r="E192" s="48"/>
       <c r="F192" s="48"/>
@@ -5370,7 +5372,7 @@
       <c r="N192" s="48"/>
       <c r="O192" s="48"/>
     </row>
-    <row r="193" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="193" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D193" s="48"/>
       <c r="E193" s="48"/>
       <c r="F193" s="48"/>
@@ -5384,7 +5386,7 @@
       <c r="N193" s="48"/>
       <c r="O193" s="48"/>
     </row>
-    <row r="194" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="194" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D194" s="48"/>
       <c r="E194" s="48"/>
       <c r="F194" s="48"/>
@@ -5398,7 +5400,7 @@
       <c r="N194" s="48"/>
       <c r="O194" s="48"/>
     </row>
-    <row r="195" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="195" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D195" s="48"/>
       <c r="E195" s="48"/>
       <c r="F195" s="48"/>
@@ -5412,7 +5414,7 @@
       <c r="N195" s="48"/>
       <c r="O195" s="48"/>
     </row>
-    <row r="196" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="196" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D196" s="48"/>
       <c r="E196" s="48"/>
       <c r="F196" s="48"/>
@@ -5426,7 +5428,7 @@
       <c r="N196" s="48"/>
       <c r="O196" s="48"/>
     </row>
-    <row r="197" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="197" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D197" s="48"/>
       <c r="E197" s="48"/>
       <c r="F197" s="48"/>
@@ -5440,7 +5442,7 @@
       <c r="N197" s="48"/>
       <c r="O197" s="48"/>
     </row>
-    <row r="198" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="198" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D198" s="48"/>
       <c r="E198" s="48"/>
       <c r="F198" s="48"/>
@@ -5454,7 +5456,7 @@
       <c r="N198" s="48"/>
       <c r="O198" s="48"/>
     </row>
-    <row r="199" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="199" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D199" s="48"/>
       <c r="E199" s="48"/>
       <c r="F199" s="48"/>
@@ -5468,7 +5470,7 @@
       <c r="N199" s="48"/>
       <c r="O199" s="48"/>
     </row>
-    <row r="200" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="200" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D200" s="48"/>
       <c r="E200" s="48"/>
       <c r="F200" s="48"/>
@@ -5482,7 +5484,7 @@
       <c r="N200" s="48"/>
       <c r="O200" s="48"/>
     </row>
-    <row r="201" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="201" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D201" s="48"/>
       <c r="E201" s="48"/>
       <c r="F201" s="48"/>
@@ -5496,7 +5498,7 @@
       <c r="N201" s="48"/>
       <c r="O201" s="48"/>
     </row>
-    <row r="202" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="202" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D202" s="48"/>
       <c r="E202" s="48"/>
       <c r="F202" s="48"/>
@@ -5510,7 +5512,7 @@
       <c r="N202" s="48"/>
       <c r="O202" s="48"/>
     </row>
-    <row r="203" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="203" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D203" s="48"/>
       <c r="E203" s="48"/>
       <c r="F203" s="48"/>
@@ -5524,7 +5526,7 @@
       <c r="N203" s="48"/>
       <c r="O203" s="48"/>
     </row>
-    <row r="204" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="204" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D204" s="48"/>
       <c r="E204" s="48"/>
       <c r="F204" s="48"/>
@@ -5538,7 +5540,7 @@
       <c r="N204" s="48"/>
       <c r="O204" s="48"/>
     </row>
-    <row r="205" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="205" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D205" s="48"/>
       <c r="E205" s="48"/>
       <c r="F205" s="48"/>
@@ -5552,7 +5554,7 @@
       <c r="N205" s="48"/>
       <c r="O205" s="48"/>
     </row>
-    <row r="206" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="206" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D206" s="48"/>
       <c r="E206" s="48"/>
       <c r="F206" s="48"/>
@@ -5566,7 +5568,7 @@
       <c r="N206" s="48"/>
       <c r="O206" s="48"/>
     </row>
-    <row r="207" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="207" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D207" s="48"/>
       <c r="E207" s="48"/>
       <c r="F207" s="48"/>
@@ -5580,7 +5582,7 @@
       <c r="N207" s="48"/>
       <c r="O207" s="48"/>
     </row>
-    <row r="208" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="208" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D208" s="48"/>
       <c r="E208" s="48"/>
       <c r="F208" s="48"/>
@@ -5594,7 +5596,7 @@
       <c r="N208" s="48"/>
       <c r="O208" s="48"/>
     </row>
-    <row r="209" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="209" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D209" s="48"/>
       <c r="E209" s="48"/>
       <c r="F209" s="48"/>
@@ -5608,7 +5610,7 @@
       <c r="N209" s="48"/>
       <c r="O209" s="48"/>
     </row>
-    <row r="210" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="210" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D210" s="48"/>
       <c r="E210" s="48"/>
       <c r="F210" s="48"/>
@@ -5622,7 +5624,7 @@
       <c r="N210" s="48"/>
       <c r="O210" s="48"/>
     </row>
-    <row r="211" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="211" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D211" s="48"/>
       <c r="E211" s="48"/>
       <c r="F211" s="48"/>
@@ -5636,7 +5638,7 @@
       <c r="N211" s="48"/>
       <c r="O211" s="48"/>
     </row>
-    <row r="212" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="212" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D212" s="48"/>
       <c r="E212" s="48"/>
       <c r="F212" s="48"/>
@@ -5650,7 +5652,7 @@
       <c r="N212" s="48"/>
       <c r="O212" s="48"/>
     </row>
-    <row r="213" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="213" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D213" s="48"/>
       <c r="E213" s="48"/>
       <c r="F213" s="48"/>
@@ -5664,7 +5666,7 @@
       <c r="N213" s="48"/>
       <c r="O213" s="48"/>
     </row>
-    <row r="214" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="214" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D214" s="48"/>
       <c r="E214" s="48"/>
       <c r="F214" s="48"/>
@@ -5678,7 +5680,7 @@
       <c r="N214" s="48"/>
       <c r="O214" s="48"/>
     </row>
-    <row r="215" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="215" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D215" s="48"/>
       <c r="E215" s="48"/>
       <c r="F215" s="48"/>
@@ -5692,7 +5694,7 @@
       <c r="N215" s="48"/>
       <c r="O215" s="48"/>
     </row>
-    <row r="216" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="216" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D216" s="48"/>
       <c r="E216" s="48"/>
       <c r="F216" s="48"/>
@@ -5706,7 +5708,7 @@
       <c r="N216" s="48"/>
       <c r="O216" s="48"/>
     </row>
-    <row r="217" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="217" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D217" s="48"/>
       <c r="E217" s="48"/>
       <c r="F217" s="48"/>
@@ -5720,7 +5722,7 @@
       <c r="N217" s="48"/>
       <c r="O217" s="48"/>
     </row>
-    <row r="218" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="218" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D218" s="48"/>
       <c r="E218" s="48"/>
       <c r="F218" s="48"/>
@@ -5734,7 +5736,7 @@
       <c r="N218" s="48"/>
       <c r="O218" s="48"/>
     </row>
-    <row r="219" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="219" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D219" s="48"/>
       <c r="E219" s="48"/>
       <c r="F219" s="48"/>
@@ -5748,7 +5750,7 @@
       <c r="N219" s="48"/>
       <c r="O219" s="48"/>
     </row>
-    <row r="220" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="220" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D220" s="48"/>
       <c r="E220" s="48"/>
       <c r="F220" s="48"/>
@@ -5762,7 +5764,7 @@
       <c r="N220" s="48"/>
       <c r="O220" s="48"/>
     </row>
-    <row r="221" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="221" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D221" s="48"/>
       <c r="E221" s="48"/>
       <c r="F221" s="48"/>
@@ -5776,7 +5778,7 @@
       <c r="N221" s="48"/>
       <c r="O221" s="48"/>
     </row>
-    <row r="222" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="222" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D222" s="48"/>
       <c r="E222" s="48"/>
       <c r="F222" s="48"/>
@@ -5790,7 +5792,7 @@
       <c r="N222" s="48"/>
       <c r="O222" s="48"/>
     </row>
-    <row r="223" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="223" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D223" s="48"/>
       <c r="E223" s="48"/>
       <c r="F223" s="48"/>
@@ -5804,7 +5806,7 @@
       <c r="N223" s="48"/>
       <c r="O223" s="48"/>
     </row>
-    <row r="224" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="224" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D224" s="48"/>
       <c r="E224" s="48"/>
       <c r="F224" s="48"/>
@@ -5818,7 +5820,7 @@
       <c r="N224" s="48"/>
       <c r="O224" s="48"/>
     </row>
-    <row r="225" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="225" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D225" s="48"/>
       <c r="E225" s="48"/>
       <c r="F225" s="48"/>
@@ -5832,7 +5834,7 @@
       <c r="N225" s="48"/>
       <c r="O225" s="48"/>
     </row>
-    <row r="226" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="226" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D226" s="48"/>
       <c r="E226" s="48"/>
       <c r="F226" s="48"/>
@@ -5846,7 +5848,7 @@
       <c r="N226" s="48"/>
       <c r="O226" s="48"/>
     </row>
-    <row r="227" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="227" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D227" s="48"/>
       <c r="E227" s="48"/>
       <c r="F227" s="48"/>
@@ -5860,7 +5862,7 @@
       <c r="N227" s="48"/>
       <c r="O227" s="48"/>
     </row>
-    <row r="228" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="228" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D228" s="48"/>
       <c r="E228" s="48"/>
       <c r="F228" s="48"/>
@@ -5874,7 +5876,7 @@
       <c r="N228" s="48"/>
       <c r="O228" s="48"/>
     </row>
-    <row r="229" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="229" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D229" s="48"/>
       <c r="E229" s="48"/>
       <c r="F229" s="48"/>
@@ -5888,7 +5890,7 @@
       <c r="N229" s="48"/>
       <c r="O229" s="48"/>
     </row>
-    <row r="230" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="230" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D230" s="48"/>
       <c r="E230" s="48"/>
       <c r="F230" s="48"/>
@@ -5902,7 +5904,7 @@
       <c r="N230" s="48"/>
       <c r="O230" s="48"/>
     </row>
-    <row r="231" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="231" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D231" s="48"/>
       <c r="E231" s="48"/>
       <c r="F231" s="48"/>
@@ -5916,7 +5918,7 @@
       <c r="N231" s="48"/>
       <c r="O231" s="48"/>
     </row>
-    <row r="232" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="232" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D232" s="48"/>
       <c r="E232" s="48"/>
       <c r="F232" s="48"/>
@@ -5930,7 +5932,7 @@
       <c r="N232" s="48"/>
       <c r="O232" s="48"/>
     </row>
-    <row r="233" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="233" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D233" s="48"/>
       <c r="E233" s="48"/>
       <c r="F233" s="48"/>
@@ -5944,7 +5946,7 @@
       <c r="N233" s="48"/>
       <c r="O233" s="48"/>
     </row>
-    <row r="234" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="234" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D234" s="48"/>
       <c r="E234" s="48"/>
       <c r="F234" s="48"/>
@@ -5958,7 +5960,7 @@
       <c r="N234" s="48"/>
       <c r="O234" s="48"/>
     </row>
-    <row r="235" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="235" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D235" s="48"/>
       <c r="E235" s="48"/>
       <c r="F235" s="48"/>
@@ -5972,7 +5974,7 @@
       <c r="N235" s="48"/>
       <c r="O235" s="48"/>
     </row>
-    <row r="236" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="236" spans="4:15" x14ac:dyDescent="0.35">
       <c r="D236" s="48"/>
       <c r="E236" s="48"/>
       <c r="F236" s="48"/>
@@ -5988,25 +5990,9 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="S65:Y65"/>
     <mergeCell ref="B65:Q66"/>
     <mergeCell ref="B67:Q68"/>
@@ -6023,12 +6009,28 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
   </mergeCells>
   <conditionalFormatting sqref="D62:Q62">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">

--- a/data/raw/51301-2026-02-medicaid.xlsx
+++ b/data/raw/51301-2026-02-medicaid.xlsx
@@ -632,51 +632,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -774,6 +774,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1122,13 +1126,13 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="92" t="s">
+      <c r="M2" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="93"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
       <c r="R2" s="4"/>
       <c r="V2" s="36"/>
       <c r="W2" s="36"/>
@@ -1205,16 +1209,16 @@
       <c r="X5" s="36"/>
     </row>
     <row r="6" spans="1:24" ht="17.600000000000001" x14ac:dyDescent="0.4">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
       <c r="I6" s="42"/>
       <c r="J6" s="42"/>
       <c r="K6" s="42"/>
@@ -1246,10 +1250,10 @@
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
       <c r="O7" s="8"/>
-      <c r="P7" s="95" t="s">
+      <c r="P7" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="Q7" s="95" t="s">
+      <c r="Q7" s="90" t="s">
         <v>37</v>
       </c>
       <c r="R7" s="4"/>
@@ -1295,8 +1299,8 @@
       <c r="O8" s="54">
         <v>2036</v>
       </c>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
+      <c r="P8" s="91"/>
+      <c r="Q8" s="91"/>
     </row>
     <row r="9" spans="1:24" ht="7.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15"/>
@@ -1318,11 +1322,11 @@
       <c r="Q9" s="45"/>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
       <c r="D10" s="57"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
@@ -1345,11 +1349,11 @@
       <c r="T10" s="7"/>
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="87"/>
-      <c r="C11" s="87"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="95"/>
       <c r="D11" s="57"/>
       <c r="E11" s="57"/>
       <c r="F11" s="57"/>
@@ -1390,11 +1394,11 @@
       <c r="T12" s="7"/>
     </row>
     <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
       <c r="D13" s="70">
         <v>668</v>
       </c>
@@ -1464,11 +1468,11 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="86" t="s">
+      <c r="A15" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
       <c r="D15" s="75"/>
       <c r="E15" s="75"/>
       <c r="F15" s="75"/>
@@ -1488,10 +1492,10 @@
       <c r="T15" s="7"/>
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="82" t="s">
+      <c r="A16" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="82"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="56"/>
       <c r="D16" s="61"/>
       <c r="E16" s="61"/>
@@ -1513,10 +1517,10 @@
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="56"/>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="84"/>
+      <c r="C17" s="83"/>
       <c r="D17" s="61"/>
       <c r="E17" s="61"/>
       <c r="F17" s="61"/>
@@ -1537,10 +1541,10 @@
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="60"/>
-      <c r="B18" s="85" t="s">
+      <c r="B18" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="85"/>
+      <c r="C18" s="94"/>
       <c r="D18" s="70">
         <v>142</v>
       </c>
@@ -1590,10 +1594,10 @@
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="56"/>
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="85"/>
+      <c r="C19" s="94"/>
       <c r="D19" s="70">
         <v>295</v>
       </c>
@@ -1642,10 +1646,10 @@
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="56"/>
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="85"/>
+      <c r="C20" s="94"/>
       <c r="D20" s="70">
         <v>16</v>
       </c>
@@ -1694,10 +1698,10 @@
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="56"/>
-      <c r="B21" s="84" t="s">
+      <c r="B21" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="84"/>
+      <c r="C21" s="83"/>
       <c r="D21" s="61"/>
       <c r="E21" s="61"/>
       <c r="F21" s="61"/>
@@ -1718,10 +1722,10 @@
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="56"/>
-      <c r="B22" s="85" t="s">
+      <c r="B22" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="85"/>
+      <c r="C22" s="94"/>
       <c r="D22" s="70">
         <v>64</v>
       </c>
@@ -1771,10 +1775,10 @@
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="56"/>
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="85"/>
+      <c r="C23" s="94"/>
       <c r="D23" s="72">
         <v>110</v>
       </c>
@@ -1895,11 +1899,11 @@
       <c r="T25" s="7"/>
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="82"/>
-      <c r="C26" s="82"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="93"/>
       <c r="D26" s="70">
         <v>8</v>
       </c>
@@ -1947,11 +1951,11 @@
       <c r="T26" s="7"/>
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="82" t="s">
+      <c r="A27" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="82"/>
-      <c r="C27" s="82"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="93"/>
       <c r="D27" s="70">
         <v>7</v>
       </c>
@@ -1999,11 +2003,11 @@
       <c r="T27" s="7"/>
     </row>
     <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="82" t="s">
+      <c r="A28" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="82"/>
-      <c r="C28" s="82"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="93"/>
       <c r="D28" s="70">
         <v>27</v>
       </c>
@@ -2096,11 +2100,11 @@
       <c r="T30" s="7"/>
     </row>
     <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="83" t="s">
+      <c r="A31" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="83"/>
-      <c r="C31" s="83"/>
+      <c r="B31" s="97"/>
+      <c r="C31" s="97"/>
       <c r="D31" s="61"/>
       <c r="E31" s="61"/>
       <c r="F31" s="61"/>
@@ -2142,13 +2146,13 @@
       <c r="T32" s="7"/>
     </row>
     <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="86" t="s">
+      <c r="A33" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
       <c r="F33" s="61"/>
       <c r="G33" s="61"/>
       <c r="H33" s="61"/>
@@ -2166,10 +2170,10 @@
       <c r="T33" s="7"/>
     </row>
     <row r="34" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="88" t="s">
+      <c r="A34" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="88"/>
+      <c r="B34" s="96"/>
       <c r="C34" s="56"/>
       <c r="D34" s="70">
         <v>125</v>
@@ -2218,11 +2222,11 @@
       <c r="T34" s="7"/>
     </row>
     <row r="35" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="84" t="s">
+      <c r="A35" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="84"/>
-      <c r="C35" s="84"/>
+      <c r="B35" s="83"/>
+      <c r="C35" s="83"/>
       <c r="D35" s="70">
         <v>191</v>
       </c>
@@ -2270,10 +2274,10 @@
       <c r="T35" s="7"/>
     </row>
     <row r="36" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B36" s="84"/>
+      <c r="B36" s="83"/>
       <c r="C36" s="56"/>
       <c r="D36" s="70">
         <v>85</v>
@@ -2322,11 +2326,11 @@
       <c r="T36" s="7"/>
     </row>
     <row r="37" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="84" t="s">
+      <c r="A37" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="84"/>
-      <c r="C37" s="84"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
       <c r="D37" s="70">
         <v>83</v>
       </c>
@@ -2374,11 +2378,11 @@
       <c r="T37" s="7"/>
     </row>
     <row r="38" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="84" t="s">
+      <c r="A38" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="84"/>
-      <c r="C38" s="84"/>
+      <c r="B38" s="83"/>
+      <c r="C38" s="83"/>
       <c r="D38" s="72">
         <v>144</v>
       </c>
@@ -2499,13 +2503,13 @@
       <c r="T40" s="7"/>
     </row>
     <row r="41" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="86" t="s">
+      <c r="A41" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86"/>
-      <c r="E41" s="86"/>
+      <c r="B41" s="82"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
       <c r="F41" s="61"/>
       <c r="G41" s="61"/>
       <c r="H41" s="61"/>
@@ -2523,10 +2527,10 @@
       <c r="T41" s="7"/>
     </row>
     <row r="42" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="84" t="s">
+      <c r="A42" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="84"/>
+      <c r="B42" s="83"/>
       <c r="C42" s="56"/>
       <c r="D42" s="70">
         <v>8</v>
@@ -2585,11 +2589,11 @@
       <c r="AD42" s="51"/>
     </row>
     <row r="43" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="84" t="s">
+      <c r="A43" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="84"/>
-      <c r="C43" s="84"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
       <c r="D43" s="70">
         <v>9</v>
       </c>
@@ -2647,10 +2651,10 @@
       <c r="AD43" s="51"/>
     </row>
     <row r="44" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="84" t="s">
+      <c r="A44" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="84"/>
+      <c r="B44" s="83"/>
       <c r="C44" s="56"/>
       <c r="D44" s="70">
         <v>31</v>
@@ -2709,11 +2713,11 @@
       <c r="AD44" s="51"/>
     </row>
     <row r="45" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="84" t="s">
+      <c r="A45" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="84"/>
-      <c r="C45" s="84"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="83"/>
       <c r="D45" s="70">
         <v>17</v>
       </c>
@@ -2771,11 +2775,11 @@
       <c r="AD45" s="51"/>
     </row>
     <row r="46" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="84" t="s">
+      <c r="A46" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="84"/>
-      <c r="C46" s="84"/>
+      <c r="B46" s="83"/>
+      <c r="C46" s="83"/>
       <c r="D46" s="72">
         <v>17</v>
       </c>
@@ -2938,11 +2942,11 @@
       <c r="T49" s="7"/>
     </row>
     <row r="50" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="86" t="s">
+      <c r="A50" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="86"/>
-      <c r="C50" s="86"/>
+      <c r="B50" s="82"/>
+      <c r="C50" s="82"/>
       <c r="D50" s="66"/>
       <c r="E50" s="66"/>
       <c r="F50" s="66"/>
@@ -2972,11 +2976,11 @@
       <c r="AD50" s="46"/>
     </row>
     <row r="51" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="84" t="s">
+      <c r="A51" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="B51" s="84"/>
-      <c r="C51" s="84"/>
+      <c r="B51" s="83"/>
+      <c r="C51" s="83"/>
       <c r="D51" s="70">
         <v>98</v>
       </c>
@@ -3066,13 +3070,13 @@
       <c r="AD52" s="46"/>
     </row>
     <row r="53" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="86" t="s">
+      <c r="A53" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="B53" s="86"/>
-      <c r="C53" s="86"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="86"/>
+      <c r="B53" s="82"/>
+      <c r="C53" s="82"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="82"/>
       <c r="F53" s="66"/>
       <c r="G53" s="66"/>
       <c r="H53" s="66"/>
@@ -3304,11 +3308,11 @@
       <c r="T57" s="7"/>
     </row>
     <row r="58" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="84" t="s">
+      <c r="A58" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="84"/>
-      <c r="C58" s="84"/>
+      <c r="B58" s="83"/>
+      <c r="C58" s="83"/>
       <c r="D58" s="70">
         <v>8670</v>
       </c>
@@ -3444,49 +3448,49 @@
       <c r="A63" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B63" s="97" t="s">
+      <c r="B63" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="C63" s="97"/>
-      <c r="D63" s="97"/>
-      <c r="E63" s="97"/>
-      <c r="F63" s="97"/>
-      <c r="G63" s="97"/>
-      <c r="H63" s="97"/>
-      <c r="I63" s="97"/>
-      <c r="J63" s="97"/>
-      <c r="K63" s="97"/>
-      <c r="L63" s="97"/>
-      <c r="M63" s="97"/>
-      <c r="N63" s="97"/>
-      <c r="O63" s="97"/>
-      <c r="P63" s="97"/>
-      <c r="Q63" s="97"/>
+      <c r="C63" s="92"/>
+      <c r="D63" s="92"/>
+      <c r="E63" s="92"/>
+      <c r="F63" s="92"/>
+      <c r="G63" s="92"/>
+      <c r="H63" s="92"/>
+      <c r="I63" s="92"/>
+      <c r="J63" s="92"/>
+      <c r="K63" s="92"/>
+      <c r="L63" s="92"/>
+      <c r="M63" s="92"/>
+      <c r="N63" s="92"/>
+      <c r="O63" s="92"/>
+      <c r="P63" s="92"/>
+      <c r="Q63" s="92"/>
       <c r="R63" s="47"/>
-      <c r="S63" s="91"/>
-      <c r="T63" s="91"/>
-      <c r="U63" s="91"/>
-      <c r="V63" s="91"/>
-      <c r="W63" s="91"/>
+      <c r="S63" s="86"/>
+      <c r="T63" s="86"/>
+      <c r="U63" s="86"/>
+      <c r="V63" s="86"/>
+      <c r="W63" s="86"/>
     </row>
     <row r="64" spans="1:30" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
-      <c r="B64" s="97"/>
-      <c r="C64" s="97"/>
-      <c r="D64" s="97"/>
-      <c r="E64" s="97"/>
-      <c r="F64" s="97"/>
-      <c r="G64" s="97"/>
-      <c r="H64" s="97"/>
-      <c r="I64" s="97"/>
-      <c r="J64" s="97"/>
-      <c r="K64" s="97"/>
-      <c r="L64" s="97"/>
-      <c r="M64" s="97"/>
-      <c r="N64" s="97"/>
-      <c r="O64" s="97"/>
-      <c r="P64" s="97"/>
-      <c r="Q64" s="97"/>
+      <c r="B64" s="92"/>
+      <c r="C64" s="92"/>
+      <c r="D64" s="92"/>
+      <c r="E64" s="92"/>
+      <c r="F64" s="92"/>
+      <c r="G64" s="92"/>
+      <c r="H64" s="92"/>
+      <c r="I64" s="92"/>
+      <c r="J64" s="92"/>
+      <c r="K64" s="92"/>
+      <c r="L64" s="92"/>
+      <c r="M64" s="92"/>
+      <c r="N64" s="92"/>
+      <c r="O64" s="92"/>
+      <c r="P64" s="92"/>
+      <c r="Q64" s="92"/>
       <c r="R64" s="47"/>
       <c r="S64" s="47"/>
     </row>
@@ -3494,51 +3498,51 @@
       <c r="A65" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B65" s="90" t="s">
+      <c r="B65" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="C65" s="90"/>
-      <c r="D65" s="90"/>
-      <c r="E65" s="90"/>
-      <c r="F65" s="90"/>
-      <c r="G65" s="90"/>
-      <c r="H65" s="90"/>
-      <c r="I65" s="90"/>
-      <c r="J65" s="90"/>
-      <c r="K65" s="90"/>
-      <c r="L65" s="90"/>
-      <c r="M65" s="90"/>
-      <c r="N65" s="90"/>
-      <c r="O65" s="90"/>
-      <c r="P65" s="90"/>
-      <c r="Q65" s="90"/>
+      <c r="C65" s="85"/>
+      <c r="D65" s="85"/>
+      <c r="E65" s="85"/>
+      <c r="F65" s="85"/>
+      <c r="G65" s="85"/>
+      <c r="H65" s="85"/>
+      <c r="I65" s="85"/>
+      <c r="J65" s="85"/>
+      <c r="K65" s="85"/>
+      <c r="L65" s="85"/>
+      <c r="M65" s="85"/>
+      <c r="N65" s="85"/>
+      <c r="O65" s="85"/>
+      <c r="P65" s="85"/>
+      <c r="Q65" s="85"/>
       <c r="R65" s="47"/>
-      <c r="S65" s="89"/>
-      <c r="T65" s="89"/>
-      <c r="U65" s="89"/>
-      <c r="V65" s="89"/>
-      <c r="W65" s="89"/>
-      <c r="X65" s="89"/>
-      <c r="Y65" s="89"/>
+      <c r="S65" s="84"/>
+      <c r="T65" s="84"/>
+      <c r="U65" s="84"/>
+      <c r="V65" s="84"/>
+      <c r="W65" s="84"/>
+      <c r="X65" s="84"/>
+      <c r="Y65" s="84"/>
     </row>
     <row r="66" spans="1:25" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
-      <c r="B66" s="90"/>
-      <c r="C66" s="90"/>
-      <c r="D66" s="90"/>
-      <c r="E66" s="90"/>
-      <c r="F66" s="90"/>
-      <c r="G66" s="90"/>
-      <c r="H66" s="90"/>
-      <c r="I66" s="90"/>
-      <c r="J66" s="90"/>
-      <c r="K66" s="90"/>
-      <c r="L66" s="90"/>
-      <c r="M66" s="90"/>
-      <c r="N66" s="90"/>
-      <c r="O66" s="90"/>
-      <c r="P66" s="90"/>
-      <c r="Q66" s="90"/>
+      <c r="B66" s="85"/>
+      <c r="C66" s="85"/>
+      <c r="D66" s="85"/>
+      <c r="E66" s="85"/>
+      <c r="F66" s="85"/>
+      <c r="G66" s="85"/>
+      <c r="H66" s="85"/>
+      <c r="I66" s="85"/>
+      <c r="J66" s="85"/>
+      <c r="K66" s="85"/>
+      <c r="L66" s="85"/>
+      <c r="M66" s="85"/>
+      <c r="N66" s="85"/>
+      <c r="O66" s="85"/>
+      <c r="P66" s="85"/>
+      <c r="Q66" s="85"/>
       <c r="R66" s="47"/>
       <c r="S66" s="47"/>
     </row>
@@ -3546,46 +3550,46 @@
       <c r="A67" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B67" s="90" t="s">
+      <c r="B67" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="90"/>
-      <c r="D67" s="90"/>
-      <c r="E67" s="90"/>
-      <c r="F67" s="90"/>
-      <c r="G67" s="90"/>
-      <c r="H67" s="90"/>
-      <c r="I67" s="90"/>
-      <c r="J67" s="90"/>
-      <c r="K67" s="90"/>
-      <c r="L67" s="90"/>
-      <c r="M67" s="90"/>
-      <c r="N67" s="90"/>
-      <c r="O67" s="90"/>
-      <c r="P67" s="90"/>
-      <c r="Q67" s="90"/>
+      <c r="C67" s="85"/>
+      <c r="D67" s="85"/>
+      <c r="E67" s="85"/>
+      <c r="F67" s="85"/>
+      <c r="G67" s="85"/>
+      <c r="H67" s="85"/>
+      <c r="I67" s="85"/>
+      <c r="J67" s="85"/>
+      <c r="K67" s="85"/>
+      <c r="L67" s="85"/>
+      <c r="M67" s="85"/>
+      <c r="N67" s="85"/>
+      <c r="O67" s="85"/>
+      <c r="P67" s="85"/>
+      <c r="Q67" s="85"/>
       <c r="R67" s="7"/>
       <c r="S67" s="4"/>
       <c r="T67" s="7"/>
     </row>
     <row r="68" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="8"/>
-      <c r="B68" s="90"/>
-      <c r="C68" s="90"/>
-      <c r="D68" s="90"/>
-      <c r="E68" s="90"/>
-      <c r="F68" s="90"/>
-      <c r="G68" s="90"/>
-      <c r="H68" s="90"/>
-      <c r="I68" s="90"/>
-      <c r="J68" s="90"/>
-      <c r="K68" s="90"/>
-      <c r="L68" s="90"/>
-      <c r="M68" s="90"/>
-      <c r="N68" s="90"/>
-      <c r="O68" s="90"/>
-      <c r="P68" s="90"/>
-      <c r="Q68" s="90"/>
+      <c r="B68" s="85"/>
+      <c r="C68" s="85"/>
+      <c r="D68" s="85"/>
+      <c r="E68" s="85"/>
+      <c r="F68" s="85"/>
+      <c r="G68" s="85"/>
+      <c r="H68" s="85"/>
+      <c r="I68" s="85"/>
+      <c r="J68" s="85"/>
+      <c r="K68" s="85"/>
+      <c r="L68" s="85"/>
+      <c r="M68" s="85"/>
+      <c r="N68" s="85"/>
+      <c r="O68" s="85"/>
+      <c r="P68" s="85"/>
+      <c r="Q68" s="85"/>
       <c r="R68" s="7"/>
       <c r="S68" s="7"/>
       <c r="T68" s="7"/>
@@ -5990,11 +5994,26 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="S65:Y65"/>
-    <mergeCell ref="B65:Q66"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="B67:Q68"/>
     <mergeCell ref="S63:W63"/>
     <mergeCell ref="M2:Q2"/>
@@ -6011,26 +6030,11 @@
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="S65:Y65"/>
+    <mergeCell ref="B65:Q66"/>
   </mergeCells>
   <conditionalFormatting sqref="D62:Q62">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
